--- a/Result/profitability/3466.xlsx
+++ b/Result/profitability/3466.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.365</v>
+        <v>-0.27375</v>
       </c>
       <c r="N2" t="n">
-        <v>-33.06875</v>
+        <v>-33.465</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2425</v>
+        <v>-0.235</v>
       </c>
       <c r="N3" t="n">
-        <v>-32.3025</v>
+        <v>-32.77875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2075</v>
+        <v>-0.1125</v>
       </c>
       <c r="N4" t="n">
-        <v>-32.60625</v>
+        <v>9.716250000000004</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0675</v>
+        <v>-0.1075</v>
       </c>
       <c r="N5" t="n">
-        <v>10.57875</v>
+        <v>10.23125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.45</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01625</v>
+        <v>-0.05375000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>10.91125</v>
+        <v>10.945</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.72</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07125000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="N7" t="n">
-        <v>11.8</v>
+        <v>14.1775</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.72</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2</v>
+        <v>0.20375</v>
       </c>
       <c r="N8" t="n">
-        <v>14.86375</v>
+        <v>15.14375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1899,10 +1899,10 @@
         <v>0.23</v>
       </c>
       <c r="M12" t="n">
-        <v>0.54125</v>
+        <v>0.5412499999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>17.24375000000001</v>
+        <v>17.24375</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>-0.35</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4874999999999999</v>
+        <v>0.4875</v>
       </c>
       <c r="N13" t="n">
         <v>17.105</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3466</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>85</v>
+      </c>
+      <c r="D75" t="n">
+        <v>76</v>
+      </c>
+      <c r="E75" t="n">
+        <v>8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-41.59%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>14</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.40375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-33.75375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02999999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.09677419354838701</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.239999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.287179487179487</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.780000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2168486739469579</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
